--- a/add_data/template_rdo_eng.xlsx
+++ b/add_data/template_rdo_eng.xlsx
@@ -1,43 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gsoraru\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{ADC04D3E-B74C-4817-B641-827B8D694759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31D9D13D-DFA9-4F90-AE98-B9C842A6134C}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{ED077C88-8821-4AA3-BBFC-E5625411D978}"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="RdO" sheetId="1" r:id="rId1"/>
+    <sheet name="RfQ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'[1]Storico offerte'!$A$407:$BA$428</definedName>
-    <definedName name="matrice">#REF!</definedName>
-  </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
 </workbook>
 </file>
@@ -48,10 +21,10 @@
     <t>Issued:</t>
   </si>
   <si>
-    <t>FULL SUPPLY</t>
-  </si>
-  <si>
-    <t>Due date:</t>
+    <t xml:space="preserve">FULL SUPPLY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Due date:</t>
   </si>
   <si>
     <t>Code</t>
@@ -63,28 +36,28 @@
     <t>Q.ty</t>
   </si>
   <si>
-    <t>Annual Q.ty</t>
+    <t xml:space="preserve">Annual Q.ty</t>
   </si>
   <si>
     <t>Description</t>
   </si>
   <si>
-    <t>Code Row material</t>
-  </si>
-  <si>
-    <t>Row material attachment</t>
-  </si>
-  <si>
-    <t>Row material supplied to be worked</t>
+    <t xml:space="preserve">Code Row material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row material attachment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row material supplied to be worked</t>
   </si>
   <si>
     <t>€/pz</t>
   </si>
   <si>
-    <t>Delivery required</t>
-  </si>
-  <si>
-    <t>Your delivery</t>
+    <t xml:space="preserve">Delivery required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your delivery</t>
   </si>
   <si>
     <t>Reference</t>
@@ -93,44 +66,47 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+  </numFmts>
   <fonts count="7">
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="11.000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="10.000000"/>
+      <color indexed="64"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="10.000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <sz val="10.000000"/>
+      <color indexed="2"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.000000"/>
+      <color indexed="2"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10.000000"/>
+      <color indexed="64"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.000000"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -144,105 +120,154 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+  <cellStyleXfs count="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="21">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="2" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="4" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="5" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="3" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="6" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="6" fillId="0" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf fontId="6" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
-    <cellStyle name="Normale_Analisi offerte GUIDO" xfId="1" xr:uid="{5E83C3D3-2722-41EF-A4C2-598764459BD7}"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -257,34 +282,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="RdO"/>
-      <sheetName val="Rdo ENG"/>
-      <sheetName val="Storico offerte"/>
-      <sheetName val="PMC"/>
-      <sheetName val="Saving Project"/>
-      <sheetName val="Stock Reduction"/>
-      <sheetName val="Pagamenti"/>
-      <sheetName val="Burgmann"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -295,48 +293,48 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Angsana New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -359,36 +357,18 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Cordia New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -411,24 +391,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -440,6 +402,231 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="New Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
                 <a:tint val="67000"/>
@@ -462,7 +649,7 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -539,7 +726,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -570,130 +757,100 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A39F4EC8-2776-4B85-B612-387E97BB77FE}">
-  <sheetPr codeName="Foglio1">
-    <tabColor rgb="FF00FF00"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:W3"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" style="13" customWidth="1"/>
-    <col min="2" max="2" width="21" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8" style="13" customWidth="1"/>
-    <col min="4" max="4" width="8" style="13" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="5" width="47.28515625" style="13" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" style="13" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="15.140625" style="14" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="35.28515625" style="15" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="4.7109375" style="13" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" style="13" customWidth="1"/>
-    <col min="11" max="11" width="10" style="13" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="13" customWidth="1"/>
-    <col min="13" max="13" width="1.7109375" style="13" customWidth="1"/>
-    <col min="14" max="16384" width="14.42578125" style="13"/>
+    <col customWidth="1" min="1" max="2" width="20.7109375"/>
+    <col customWidth="1" min="3" max="4" width="10.7109375"/>
+    <col customWidth="1" min="5" max="5" width="40.7109375"/>
+    <col customWidth="1" min="6" max="7" width="20.7109375"/>
+    <col customWidth="1" min="8" max="8" width="40.7109375"/>
+    <col customWidth="1" min="9" max="12" width="10.7109375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="5" customFormat="1" ht="12.75">
+    <row r="1" ht="14.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
-      <c r="C1" s="19"/>
+      <c r="C1" s="3"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="4"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="6"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="9"/>
     </row>
-    <row r="2" spans="1:23" s="5" customFormat="1" ht="12.75">
-      <c r="A2" s="7" t="s">
+    <row r="2" ht="14.25">
+      <c r="A2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="12"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="17"/>
     </row>
-    <row r="3" spans="1:23" s="11" customFormat="1" ht="51" customHeight="1">
-      <c r="A3" s="16" t="s">
+    <row r="3" ht="27">
+      <c r="A3" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="J3" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="K3" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="18" t="s">
+      <c r="L3" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
-      <c r="V3" s="10"/>
-      <c r="W3" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C1:C2"/>
   </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;A&amp;R000000Document classified as: 4 - Protected#</oddHeader>
-    <oddFooter>&amp;CPagina &amp;P</oddFooter>
-  </headerFooter>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/add_data/template_rdo_eng.xlsx
+++ b/add_data/template_rdo_eng.xlsx
@@ -70,7 +70,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -79,13 +79,8 @@
     </font>
     <font>
       <sz val="10.000000"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.000000"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -98,11 +93,6 @@
       <sz val="10.000000"/>
       <color indexed="2"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10.000000"/>
-      <color indexed="64"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -150,7 +140,7 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
+      <bottom/>
       <diagonal style="none"/>
     </border>
     <border>
@@ -203,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -211,34 +201,31 @@
     <xf fontId="1" fillId="0" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="2" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
     <xf fontId="1" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="4" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="5" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -250,20 +237,20 @@
     <xf fontId="1" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf fontId="1" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
     <xf fontId="1" fillId="0" borderId="3" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf fontId="6" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="6" fillId="0" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="6" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -767,9 +754,7 @@
     <col customWidth="1" min="1" max="2" width="20.7109375"/>
     <col customWidth="1" min="3" max="4" width="10.7109375"/>
     <col customWidth="1" min="5" max="5" width="40.7109375"/>
-    <col customWidth="1" min="6" max="7" width="20.7109375"/>
-    <col customWidth="1" min="8" max="8" width="40.7109375"/>
-    <col customWidth="1" min="9" max="12" width="10.7109375"/>
+    <col customWidth="1" min="6" max="9" width="10.7109375"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
@@ -788,47 +773,47 @@
       <c r="I1" s="7"/>
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
-      <c r="L1" s="9"/>
+      <c r="L1" s="7"/>
     </row>
     <row r="2" ht="14.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="14"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="15"/>
       <c r="J2" s="16"/>
       <c r="K2" s="16"/>
-      <c r="L2" s="17"/>
+      <c r="L2" s="15"/>
     </row>
-    <row r="3" ht="27">
-      <c r="A3" s="18" t="s">
+    <row r="3" ht="54">
+      <c r="A3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="17" t="s">
         <v>10</v>
       </c>
       <c r="I3" s="18" t="s">
@@ -840,7 +825,7 @@
       <c r="K3" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="20" t="s">
+      <c r="L3" s="18" t="s">
         <v>14</v>
       </c>
     </row>

--- a/add_data/template_rdo_eng.xlsx
+++ b/add_data/template_rdo_eng.xlsx
@@ -1,43 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gsoraru\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{ADC04D3E-B74C-4817-B641-827B8D694759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31D9D13D-DFA9-4F90-AE98-B9C842A6134C}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{ED077C88-8821-4AA3-BBFC-E5625411D978}"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="RdO" sheetId="1" r:id="rId1"/>
+    <sheet name="RfQ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'[1]Storico offerte'!$A$407:$BA$428</definedName>
-    <definedName name="matrice">#REF!</definedName>
-  </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
 </workbook>
 </file>
@@ -48,10 +21,10 @@
     <t>Issued:</t>
   </si>
   <si>
-    <t>FULL SUPPLY</t>
-  </si>
-  <si>
-    <t>Due date:</t>
+    <t xml:space="preserve">FULL SUPPLY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Due date:</t>
   </si>
   <si>
     <t>Code</t>
@@ -63,28 +36,28 @@
     <t>Q.ty</t>
   </si>
   <si>
-    <t>Annual Q.ty</t>
+    <t xml:space="preserve">Annual Q.ty</t>
   </si>
   <si>
     <t>Description</t>
   </si>
   <si>
-    <t>Code Row material</t>
-  </si>
-  <si>
-    <t>Row material attachment</t>
-  </si>
-  <si>
-    <t>Row material supplied to be worked</t>
+    <t xml:space="preserve">Code Row material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row material attachment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Row material supplied to be worked</t>
   </si>
   <si>
     <t>€/pz</t>
   </si>
   <si>
-    <t>Delivery required</t>
-  </si>
-  <si>
-    <t>Your delivery</t>
+    <t xml:space="preserve">Delivery required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your delivery</t>
   </si>
   <si>
     <t>Reference</t>
@@ -93,44 +66,37 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+  </numFmts>
+  <fonts count="5">
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="11.000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="10.000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="10.000000"/>
+      <color indexed="2"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <sz val="10.000000"/>
+      <color indexed="2"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.000000"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -144,105 +110,151 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+  <cellStyleXfs count="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="20">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="1" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="1" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="4" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="1" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="3" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="5" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
-    <cellStyle name="Normale_Analisi offerte GUIDO" xfId="1" xr:uid="{5E83C3D3-2722-41EF-A4C2-598764459BD7}"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -257,34 +269,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="RdO"/>
-      <sheetName val="Rdo ENG"/>
-      <sheetName val="Storico offerte"/>
-      <sheetName val="PMC"/>
-      <sheetName val="Saving Project"/>
-      <sheetName val="Stock Reduction"/>
-      <sheetName val="Pagamenti"/>
-      <sheetName val="Burgmann"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -295,48 +280,48 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Angsana New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -359,36 +344,18 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Cordia New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -411,24 +378,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -440,6 +389,231 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="New Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
                 <a:tint val="67000"/>
@@ -462,7 +636,7 @@
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -539,7 +713,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -570,130 +744,98 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A39F4EC8-2776-4B85-B612-387E97BB77FE}">
-  <sheetPr codeName="Foglio1">
-    <tabColor rgb="FF00FF00"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:W3"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" outlineLevelCol="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" style="13" customWidth="1"/>
-    <col min="2" max="2" width="21" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8" style="13" customWidth="1"/>
-    <col min="4" max="4" width="8" style="13" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="5" width="47.28515625" style="13" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" style="13" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="15.140625" style="14" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="35.28515625" style="15" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="4.7109375" style="13" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" style="13" customWidth="1"/>
-    <col min="11" max="11" width="10" style="13" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="13" customWidth="1"/>
-    <col min="13" max="13" width="1.7109375" style="13" customWidth="1"/>
-    <col min="14" max="16384" width="14.42578125" style="13"/>
+    <col customWidth="1" min="1" max="2" width="20.7109375"/>
+    <col customWidth="1" min="3" max="4" width="10.7109375"/>
+    <col customWidth="1" min="5" max="5" width="40.7109375"/>
+    <col customWidth="1" min="6" max="9" width="10.7109375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="5" customFormat="1" ht="12.75">
+    <row r="1" ht="14.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
-      <c r="C1" s="19"/>
+      <c r="C1" s="3"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="4"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="6"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="7"/>
     </row>
-    <row r="2" spans="1:23" s="5" customFormat="1" ht="12.75">
-      <c r="A2" s="7" t="s">
+    <row r="2" ht="14.25">
+      <c r="A2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="12"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="15"/>
     </row>
-    <row r="3" spans="1:23" s="11" customFormat="1" ht="51" customHeight="1">
-      <c r="A3" s="16" t="s">
+    <row r="3" ht="54">
+      <c r="A3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="I3" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="J3" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="K3" s="19" t="s">
         <v>13</v>
       </c>
       <c r="L3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
-      <c r="V3" s="10"/>
-      <c r="W3" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C1:C2"/>
   </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;A&amp;R000000Document classified as: 4 - Protected#</oddHeader>
-    <oddFooter>&amp;CPagina &amp;P</oddFooter>
-  </headerFooter>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
 </worksheet>
 </file>